--- a/output/stock_quant_scores/JPM_income_df.xlsx
+++ b/output/stock_quant_scores/JPM_income_df.xlsx
@@ -1112,12 +1112,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>15.39</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>48334000000</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1133,7 +1137,9 @@
         <v>10338000000</v>
       </c>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>121685000000</v>
+      </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
